--- a/ANE21_PCB_NogTeHalen.csv.xlsx
+++ b/ANE21_PCB_NogTeHalen.csv.xlsx
@@ -8,21 +8,23 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\koeki\Documents\GitHub\ANE21_PCB\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7C4461FB-05BB-4524-BF2A-4E8E4DEFE96B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB87E2AC-53CC-4E73-A95A-A40A7DA90CBE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{1211B9E7-5962-410F-9B7F-7E5856436F3B}"/>
+    <workbookView minimized="1" xWindow="390" yWindow="390" windowWidth="21600" windowHeight="11295" activeTab="1" xr2:uid="{1211B9E7-5962-410F-9B7F-7E5856436F3B}"/>
   </bookViews>
   <sheets>
     <sheet name="ANE21_PCB" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet2" sheetId="3" r:id="rId3"/>
+    <sheet name="PerSide" sheetId="5" r:id="rId2"/>
+    <sheet name="Sheet1" sheetId="2" r:id="rId3"/>
+    <sheet name="Sheet3" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet2" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="317" uniqueCount="159">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="429" uniqueCount="163">
   <si>
     <t>Reference</t>
   </si>
@@ -499,6 +501,18 @@
   </si>
   <si>
     <t>https://nl.farnell.com/en-NL/multicomp-pro/2213s-12g/header-2-row-vert-12way/dp/1593443</t>
+  </si>
+  <si>
+    <t>Nodig</t>
+  </si>
+  <si>
+    <t>Eén PCB</t>
+  </si>
+  <si>
+    <t>https://nl.farnell.com/alcoswitch-te-connectivity/147873-1/tactile-switch-spst-0-05a-24v/dp/2610942</t>
+  </si>
+  <si>
+    <t>PCIe side</t>
   </si>
 </sst>
 </file>
@@ -1942,6 +1956,346 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{834F74BB-44EB-426C-A46C-C99CD43ED2DB}">
+  <dimension ref="A1:G28"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="33.5703125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2">
+        <v>2</v>
+      </c>
+      <c r="C2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+      <c r="C3" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>14</v>
+      </c>
+      <c r="B4">
+        <v>2</v>
+      </c>
+      <c r="C4" t="s">
+        <v>15</v>
+      </c>
+      <c r="G4" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>16</v>
+      </c>
+      <c r="B5">
+        <v>2</v>
+      </c>
+      <c r="C5" t="s">
+        <v>17</v>
+      </c>
+      <c r="G5" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>18</v>
+      </c>
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" t="s">
+        <v>19</v>
+      </c>
+      <c r="G6" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>20</v>
+      </c>
+      <c r="B7">
+        <v>4</v>
+      </c>
+      <c r="C7" t="s">
+        <v>21</v>
+      </c>
+      <c r="G7" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>22</v>
+      </c>
+      <c r="B8">
+        <v>3</v>
+      </c>
+      <c r="C8" t="s">
+        <v>23</v>
+      </c>
+      <c r="G8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>25</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>31</v>
+      </c>
+      <c r="B11">
+        <v>1</v>
+      </c>
+      <c r="C11" t="s">
+        <v>32</v>
+      </c>
+      <c r="G11" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>34</v>
+      </c>
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" t="s">
+        <v>35</v>
+      </c>
+      <c r="G12" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A14" t="s">
+        <v>41</v>
+      </c>
+      <c r="B14">
+        <v>1</v>
+      </c>
+      <c r="C14" t="s">
+        <v>42</v>
+      </c>
+      <c r="G14" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A15" t="s">
+        <v>44</v>
+      </c>
+      <c r="B15">
+        <v>1</v>
+      </c>
+      <c r="C15" t="s">
+        <v>45</v>
+      </c>
+      <c r="G15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A16" t="s">
+        <v>97</v>
+      </c>
+      <c r="B16">
+        <v>1</v>
+      </c>
+      <c r="C16" t="s">
+        <v>32</v>
+      </c>
+      <c r="G16" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A17" t="s">
+        <v>47</v>
+      </c>
+      <c r="B17">
+        <v>1</v>
+      </c>
+      <c r="C17" t="s">
+        <v>48</v>
+      </c>
+      <c r="G17" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18">
+        <v>2</v>
+      </c>
+      <c r="C18" t="s">
+        <v>51</v>
+      </c>
+      <c r="G18" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20">
+        <v>4</v>
+      </c>
+      <c r="C20" t="s">
+        <v>57</v>
+      </c>
+      <c r="G20" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>59</v>
+      </c>
+      <c r="B21">
+        <v>2</v>
+      </c>
+      <c r="C21" t="s">
+        <v>60</v>
+      </c>
+      <c r="G21" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A22" t="s">
+        <v>61</v>
+      </c>
+      <c r="B22">
+        <v>1</v>
+      </c>
+      <c r="C22" t="s">
+        <v>62</v>
+      </c>
+      <c r="G22" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A23" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23">
+        <v>1</v>
+      </c>
+      <c r="C23" t="s">
+        <v>64</v>
+      </c>
+      <c r="G23" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24">
+        <v>2</v>
+      </c>
+      <c r="C24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G24" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A25" t="s">
+        <v>67</v>
+      </c>
+      <c r="B25">
+        <v>1</v>
+      </c>
+      <c r="C25" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" t="s">
+        <v>58</v>
+      </c>
+    </row>
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A26" t="s">
+        <v>69</v>
+      </c>
+      <c r="B26">
+        <v>3</v>
+      </c>
+      <c r="C26" t="s">
+        <v>70</v>
+      </c>
+      <c r="G26" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A28" t="s">
+        <v>75</v>
+      </c>
+      <c r="B28">
+        <v>1</v>
+      </c>
+      <c r="C28" t="s">
+        <v>76</v>
+      </c>
+      <c r="G28" t="s">
+        <v>77</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BEF26D9D-FC33-44FC-8DF1-800D76A96D71}">
   <dimension ref="A1:E58"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2665,7 +3019,233 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2F138570-7E2E-44C5-973D-96B1C817B119}">
+  <dimension ref="A1:F11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.42578125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.28515625" customWidth="1"/>
+    <col min="3" max="3" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="70" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="104.42578125" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="1"/>
+      <c r="B1" s="1" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>159</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>110</v>
+      </c>
+      <c r="B3">
+        <v>2</v>
+      </c>
+      <c r="C3">
+        <v>7</v>
+      </c>
+      <c r="D3" t="s">
+        <v>51</v>
+      </c>
+      <c r="E3" t="s">
+        <v>52</v>
+      </c>
+      <c r="F3" s="2" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>148</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
+      </c>
+      <c r="D4" t="s">
+        <v>151</v>
+      </c>
+      <c r="E4" t="s">
+        <v>24</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>149</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
+      </c>
+      <c r="D5" t="s">
+        <v>152</v>
+      </c>
+      <c r="E5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F5" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>150</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+      <c r="C6">
+        <v>10</v>
+      </c>
+      <c r="D6" t="s">
+        <v>153</v>
+      </c>
+      <c r="E6" t="s">
+        <v>24</v>
+      </c>
+      <c r="F6" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>25</v>
+      </c>
+      <c r="B7">
+        <v>1</v>
+      </c>
+      <c r="C7">
+        <v>10</v>
+      </c>
+      <c r="D7" t="s">
+        <v>26</v>
+      </c>
+      <c r="E7" t="s">
+        <v>27</v>
+      </c>
+      <c r="F7" s="2" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>41</v>
+      </c>
+      <c r="B8">
+        <v>1</v>
+      </c>
+      <c r="C8">
+        <v>10</v>
+      </c>
+      <c r="D8" t="s">
+        <v>42</v>
+      </c>
+      <c r="E8" t="s">
+        <v>43</v>
+      </c>
+      <c r="F8" s="2" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>47</v>
+      </c>
+      <c r="B9">
+        <v>1</v>
+      </c>
+      <c r="C9">
+        <v>10</v>
+      </c>
+      <c r="D9" t="s">
+        <v>48</v>
+      </c>
+      <c r="E9" t="s">
+        <v>49</v>
+      </c>
+      <c r="F9" s="2" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>69</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="C10">
+        <v>10</v>
+      </c>
+      <c r="D10" t="s">
+        <v>70</v>
+      </c>
+      <c r="E10" t="s">
+        <v>71</v>
+      </c>
+      <c r="F10" s="2" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1</v>
+      </c>
+      <c r="C11">
+        <v>0</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>98</v>
+      </c>
+      <c r="F11" s="2" t="s">
+        <v>128</v>
+      </c>
+    </row>
+  </sheetData>
+  <hyperlinks>
+    <hyperlink ref="F11" r:id="rId1" xr:uid="{0CC27E64-3325-463C-A84D-5B67107BBB98}"/>
+    <hyperlink ref="F3" r:id="rId2" xr:uid="{83EC8F65-BB27-4B80-85D1-FA1FA1F3F0E1}"/>
+    <hyperlink ref="F7" r:id="rId3" xr:uid="{AD67330E-B0ED-4807-8AB8-22E56A9094B1}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA091CD4-5094-4710-9209-4E90DC99F389}">
   <dimension ref="A1:G14"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -2832,14 +3412,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <_activity xmlns="e29b34d8-3881-4d6b-9d28-27e301936cd4" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100E849CDDC7387BA4191402651B8127538" ma:contentTypeVersion="15" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="badf7a6c7ba6a7e1b6fc85107a15e429">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns3="5c04733c-0184-4690-87f6-d82611266225" xmlns:ns4="e29b34d8-3881-4d6b-9d28-27e301936cd4" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c0f6749e73180a912996a88793d0f2b2" ns3:_="" ns4:_="">
     <xsd:import namespace="5c04733c-0184-4690-87f6-d82611266225"/>
@@ -3072,6 +3644,14 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <_activity xmlns="e29b34d8-3881-4d6b-9d28-27e301936cd4" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -3082,23 +3662,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55E24BAC-F733-491B-9E1B-E51FCFD602AB}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="e29b34d8-3881-4d6b-9d28-27e301936cd4"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="5c04733c-0184-4690-87f6-d82611266225"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{87D424C8-70CC-4647-92A0-1F14375FA407}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -3117,6 +3680,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{55E24BAC-F733-491B-9E1B-E51FCFD602AB}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="e29b34d8-3881-4d6b-9d28-27e301936cd4"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="5c04733c-0184-4690-87f6-d82611266225"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{19D80ACF-8CFC-432A-B1AE-2EAB842C2B3D}">
   <ds:schemaRefs>
